--- a/raw/processedSamples/20260422_r9_DB_USDA-nasal-swabs_RT-QuIC.xlsx
+++ b/raw/processedSamples/20260422_r9_DB_USDA-nasal-swabs_RT-QuIC.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gage1\Box\MNPRO\RT-QuIC\RT-QuIC Data\Damani's RT-QuIC Runs\2026 USDA Files\20260422\20260422_r9_DB_USDA-nasal-swabs_RT-QuIC\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rowde002\Documents\Projects\usda-validation\raw\processedSamples\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32FAB649-1F94-4F5D-85A1-AC23D0EDE274}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{413994DA-D564-4975-8306-D1B1AD1A3738}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5100" yWindow="3900" windowWidth="21600" windowHeight="11295" xr2:uid="{35DA0389-4C4F-4251-9C66-54A4FA602C12}"/>
+    <workbookView xWindow="-28920" yWindow="-15" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{35DA0389-4C4F-4251-9C66-54A4FA602C12}"/>
   </bookViews>
   <sheets>
     <sheet name="Microplate Cycle 1 (0 h)" sheetId="2" r:id="rId1"/>
@@ -32,12 +32,15 @@
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="723" uniqueCount="192">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="723" uniqueCount="170">
   <si>
     <t>User: USER</t>
   </si>
@@ -444,73 +447,7 @@
     <t>P</t>
   </si>
   <si>
-    <t>1917-S</t>
-  </si>
-  <si>
-    <t>1918-S</t>
-  </si>
-  <si>
-    <t>1919-S</t>
-  </si>
-  <si>
-    <t>1920-S</t>
-  </si>
-  <si>
-    <t>1921-S</t>
-  </si>
-  <si>
-    <t>1922-S</t>
-  </si>
-  <si>
-    <t>1923-S</t>
-  </si>
-  <si>
-    <t>1924-S</t>
-  </si>
-  <si>
-    <t>1925-S</t>
-  </si>
-  <si>
-    <t>1926-S</t>
-  </si>
-  <si>
-    <t>1927-S</t>
-  </si>
-  <si>
     <t>N</t>
-  </si>
-  <si>
-    <t>1928-S</t>
-  </si>
-  <si>
-    <t>1929-S</t>
-  </si>
-  <si>
-    <t>1930-S</t>
-  </si>
-  <si>
-    <t>1931-S</t>
-  </si>
-  <si>
-    <t>1932-S</t>
-  </si>
-  <si>
-    <t>1933-S</t>
-  </si>
-  <si>
-    <t>1934-S</t>
-  </si>
-  <si>
-    <t>1935-S</t>
-  </si>
-  <si>
-    <t>1936-S</t>
-  </si>
-  <si>
-    <t>1937-S</t>
-  </si>
-  <si>
-    <t>1938-S</t>
   </si>
   <si>
     <t>1. Sample IDs</t>
@@ -1286,7 +1223,7 @@
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
-        <v>158</v>
+        <v>136</v>
       </c>
       <c r="O14" s="18"/>
     </row>
@@ -1328,341 +1265,341 @@
         <v>12</v>
       </c>
       <c r="O15" s="19" t="s">
-        <v>167</v>
+        <v>145</v>
       </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="9" t="s">
-        <v>159</v>
+        <v>137</v>
       </c>
       <c r="B16" s="10" t="s">
         <v>134</v>
       </c>
       <c r="C16" s="11" t="s">
-        <v>170</v>
+        <v>148</v>
       </c>
       <c r="D16" s="11" t="s">
-        <v>171</v>
+        <v>149</v>
       </c>
       <c r="E16" s="11" t="s">
-        <v>172</v>
+        <v>150</v>
       </c>
       <c r="F16" s="11" t="s">
-        <v>173</v>
+        <v>151</v>
       </c>
       <c r="G16" s="11" t="s">
-        <v>174</v>
+        <v>152</v>
       </c>
       <c r="H16" s="11" t="s">
-        <v>175</v>
+        <v>153</v>
       </c>
       <c r="I16" s="11" t="s">
-        <v>176</v>
+        <v>154</v>
       </c>
       <c r="J16" s="11" t="s">
-        <v>177</v>
+        <v>155</v>
       </c>
       <c r="K16" s="11" t="s">
-        <v>178</v>
+        <v>156</v>
       </c>
       <c r="L16" s="11" t="s">
-        <v>179</v>
+        <v>157</v>
       </c>
       <c r="M16" s="11" t="s">
-        <v>180</v>
+        <v>158</v>
       </c>
       <c r="O16" s="20"/>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" s="9" t="s">
-        <v>160</v>
+        <v>138</v>
       </c>
       <c r="B17" s="4" t="s">
         <v>134</v>
       </c>
       <c r="C17" s="11" t="s">
-        <v>170</v>
+        <v>148</v>
       </c>
       <c r="D17" s="11" t="s">
-        <v>171</v>
+        <v>149</v>
       </c>
       <c r="E17" s="11" t="s">
-        <v>172</v>
+        <v>150</v>
       </c>
       <c r="F17" s="11" t="s">
-        <v>173</v>
+        <v>151</v>
       </c>
       <c r="G17" s="11" t="s">
-        <v>174</v>
+        <v>152</v>
       </c>
       <c r="H17" s="11" t="s">
-        <v>175</v>
+        <v>153</v>
       </c>
       <c r="I17" s="11" t="s">
-        <v>176</v>
+        <v>154</v>
       </c>
       <c r="J17" s="11" t="s">
-        <v>177</v>
+        <v>155</v>
       </c>
       <c r="K17" s="11" t="s">
-        <v>178</v>
+        <v>156</v>
       </c>
       <c r="L17" s="11" t="s">
-        <v>179</v>
+        <v>157</v>
       </c>
       <c r="M17" s="11" t="s">
-        <v>180</v>
+        <v>158</v>
       </c>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" s="9" t="s">
-        <v>161</v>
+        <v>139</v>
       </c>
       <c r="B18" s="4" t="s">
         <v>134</v>
       </c>
       <c r="C18" s="11" t="s">
-        <v>170</v>
+        <v>148</v>
       </c>
       <c r="D18" s="11" t="s">
-        <v>171</v>
+        <v>149</v>
       </c>
       <c r="E18" s="11" t="s">
-        <v>172</v>
+        <v>150</v>
       </c>
       <c r="F18" s="11" t="s">
-        <v>173</v>
+        <v>151</v>
       </c>
       <c r="G18" s="11" t="s">
-        <v>174</v>
+        <v>152</v>
       </c>
       <c r="H18" s="11" t="s">
-        <v>175</v>
+        <v>153</v>
       </c>
       <c r="I18" s="11" t="s">
-        <v>176</v>
+        <v>154</v>
       </c>
       <c r="J18" s="11" t="s">
-        <v>177</v>
+        <v>155</v>
       </c>
       <c r="K18" s="11" t="s">
-        <v>178</v>
+        <v>156</v>
       </c>
       <c r="L18" s="11" t="s">
-        <v>179</v>
+        <v>157</v>
       </c>
       <c r="M18" s="11" t="s">
-        <v>180</v>
+        <v>158</v>
       </c>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" s="9" t="s">
-        <v>162</v>
+        <v>140</v>
       </c>
       <c r="B19" s="4" t="s">
         <v>134</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>170</v>
+        <v>148</v>
       </c>
       <c r="D19" s="11" t="s">
-        <v>171</v>
+        <v>149</v>
       </c>
       <c r="E19" s="11" t="s">
-        <v>172</v>
+        <v>150</v>
       </c>
       <c r="F19" s="11" t="s">
-        <v>173</v>
+        <v>151</v>
       </c>
       <c r="G19" s="11" t="s">
-        <v>174</v>
+        <v>152</v>
       </c>
       <c r="H19" s="11" t="s">
-        <v>175</v>
+        <v>153</v>
       </c>
       <c r="I19" s="11" t="s">
-        <v>176</v>
+        <v>154</v>
       </c>
       <c r="J19" s="11" t="s">
-        <v>177</v>
+        <v>155</v>
       </c>
       <c r="K19" s="11" t="s">
-        <v>178</v>
+        <v>156</v>
       </c>
       <c r="L19" s="11" t="s">
-        <v>179</v>
+        <v>157</v>
       </c>
       <c r="M19" s="11" t="s">
-        <v>180</v>
+        <v>158</v>
       </c>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" s="9" t="s">
+        <v>141</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="C20" s="13" t="s">
+        <v>159</v>
+      </c>
+      <c r="D20" s="13" t="s">
+        <v>160</v>
+      </c>
+      <c r="E20" s="13" t="s">
+        <v>161</v>
+      </c>
+      <c r="F20" s="13" t="s">
+        <v>162</v>
+      </c>
+      <c r="G20" s="13" t="s">
         <v>163</v>
       </c>
-      <c r="B20" s="4" t="s">
-        <v>146</v>
-      </c>
-      <c r="C20" s="13" t="s">
-        <v>181</v>
-      </c>
-      <c r="D20" s="13" t="s">
-        <v>182</v>
-      </c>
-      <c r="E20" s="13" t="s">
-        <v>183</v>
-      </c>
-      <c r="F20" s="13" t="s">
-        <v>184</v>
-      </c>
-      <c r="G20" s="13" t="s">
-        <v>185</v>
-      </c>
       <c r="H20" s="13" t="s">
-        <v>186</v>
+        <v>164</v>
       </c>
       <c r="I20" s="13" t="s">
-        <v>187</v>
+        <v>165</v>
       </c>
       <c r="J20" s="13" t="s">
-        <v>188</v>
+        <v>166</v>
       </c>
       <c r="K20" s="13" t="s">
-        <v>189</v>
+        <v>167</v>
       </c>
       <c r="L20" s="13" t="s">
-        <v>190</v>
+        <v>168</v>
       </c>
       <c r="M20" s="13" t="s">
-        <v>191</v>
+        <v>169</v>
       </c>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="C21" s="13" t="s">
+        <v>159</v>
+      </c>
+      <c r="D21" s="13" t="s">
+        <v>160</v>
+      </c>
+      <c r="E21" s="13" t="s">
+        <v>161</v>
+      </c>
+      <c r="F21" s="13" t="s">
+        <v>162</v>
+      </c>
+      <c r="G21" s="13" t="s">
+        <v>163</v>
+      </c>
+      <c r="H21" s="13" t="s">
         <v>164</v>
       </c>
-      <c r="B21" s="4" t="s">
-        <v>146</v>
-      </c>
-      <c r="C21" s="13" t="s">
-        <v>181</v>
-      </c>
-      <c r="D21" s="13" t="s">
-        <v>182</v>
-      </c>
-      <c r="E21" s="13" t="s">
-        <v>183</v>
-      </c>
-      <c r="F21" s="13" t="s">
-        <v>184</v>
-      </c>
-      <c r="G21" s="13" t="s">
-        <v>185</v>
-      </c>
-      <c r="H21" s="13" t="s">
-        <v>186</v>
-      </c>
       <c r="I21" s="13" t="s">
-        <v>187</v>
+        <v>165</v>
       </c>
       <c r="J21" s="13" t="s">
-        <v>188</v>
+        <v>166</v>
       </c>
       <c r="K21" s="13" t="s">
-        <v>189</v>
+        <v>167</v>
       </c>
       <c r="L21" s="13" t="s">
-        <v>190</v>
+        <v>168</v>
       </c>
       <c r="M21" s="13" t="s">
-        <v>191</v>
+        <v>169</v>
       </c>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" s="9" t="s">
+        <v>143</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="C22" s="13" t="s">
+        <v>159</v>
+      </c>
+      <c r="D22" s="13" t="s">
+        <v>160</v>
+      </c>
+      <c r="E22" s="13" t="s">
+        <v>161</v>
+      </c>
+      <c r="F22" s="13" t="s">
+        <v>162</v>
+      </c>
+      <c r="G22" s="13" t="s">
+        <v>163</v>
+      </c>
+      <c r="H22" s="13" t="s">
+        <v>164</v>
+      </c>
+      <c r="I22" s="13" t="s">
         <v>165</v>
       </c>
-      <c r="B22" s="4" t="s">
-        <v>146</v>
-      </c>
-      <c r="C22" s="13" t="s">
-        <v>181</v>
-      </c>
-      <c r="D22" s="13" t="s">
-        <v>182</v>
-      </c>
-      <c r="E22" s="13" t="s">
-        <v>183</v>
-      </c>
-      <c r="F22" s="13" t="s">
-        <v>184</v>
-      </c>
-      <c r="G22" s="13" t="s">
-        <v>185</v>
-      </c>
-      <c r="H22" s="13" t="s">
-        <v>186</v>
-      </c>
-      <c r="I22" s="13" t="s">
-        <v>187</v>
-      </c>
       <c r="J22" s="13" t="s">
-        <v>188</v>
+        <v>166</v>
       </c>
       <c r="K22" s="13" t="s">
-        <v>189</v>
+        <v>167</v>
       </c>
       <c r="L22" s="13" t="s">
-        <v>190</v>
+        <v>168</v>
       </c>
       <c r="M22" s="13" t="s">
-        <v>191</v>
+        <v>169</v>
       </c>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" s="9" t="s">
+        <v>144</v>
+      </c>
+      <c r="B23" s="15" t="s">
+        <v>135</v>
+      </c>
+      <c r="C23" s="13" t="s">
+        <v>159</v>
+      </c>
+      <c r="D23" s="13" t="s">
+        <v>160</v>
+      </c>
+      <c r="E23" s="13" t="s">
+        <v>161</v>
+      </c>
+      <c r="F23" s="13" t="s">
+        <v>162</v>
+      </c>
+      <c r="G23" s="13" t="s">
+        <v>163</v>
+      </c>
+      <c r="H23" s="13" t="s">
+        <v>164</v>
+      </c>
+      <c r="I23" s="13" t="s">
+        <v>165</v>
+      </c>
+      <c r="J23" s="13" t="s">
         <v>166</v>
       </c>
-      <c r="B23" s="15" t="s">
-        <v>146</v>
-      </c>
-      <c r="C23" s="13" t="s">
-        <v>181</v>
-      </c>
-      <c r="D23" s="13" t="s">
-        <v>182</v>
-      </c>
-      <c r="E23" s="13" t="s">
-        <v>183</v>
-      </c>
-      <c r="F23" s="13" t="s">
-        <v>184</v>
-      </c>
-      <c r="G23" s="13" t="s">
-        <v>185</v>
-      </c>
-      <c r="H23" s="13" t="s">
-        <v>186</v>
-      </c>
-      <c r="I23" s="13" t="s">
-        <v>187</v>
-      </c>
-      <c r="J23" s="13" t="s">
-        <v>188</v>
-      </c>
       <c r="K23" s="13" t="s">
-        <v>189</v>
+        <v>167</v>
       </c>
       <c r="L23" s="13" t="s">
-        <v>190</v>
+        <v>168</v>
       </c>
       <c r="M23" s="13" t="s">
-        <v>191</v>
+        <v>169</v>
       </c>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B25" t="s">
-        <v>168</v>
+        <v>146</v>
       </c>
       <c r="O25" s="18"/>
     </row>
@@ -1704,12 +1641,12 @@
         <v>12</v>
       </c>
       <c r="O26" s="19" t="s">
-        <v>167</v>
+        <v>145</v>
       </c>
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" s="9" t="s">
-        <v>159</v>
+        <v>137</v>
       </c>
       <c r="B27" s="10">
         <v>1000</v>
@@ -1751,7 +1688,7 @@
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" s="9" t="s">
-        <v>160</v>
+        <v>138</v>
       </c>
       <c r="B28" s="4">
         <v>1000</v>
@@ -1792,7 +1729,7 @@
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" s="9" t="s">
-        <v>161</v>
+        <v>139</v>
       </c>
       <c r="B29" s="4">
         <v>1000</v>
@@ -1833,7 +1770,7 @@
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" s="9" t="s">
-        <v>162</v>
+        <v>140</v>
       </c>
       <c r="B30" s="4">
         <v>1000</v>
@@ -1874,7 +1811,7 @@
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" s="9" t="s">
-        <v>163</v>
+        <v>141</v>
       </c>
       <c r="B31" s="4">
         <v>1000</v>
@@ -1915,7 +1852,7 @@
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" s="9" t="s">
-        <v>164</v>
+        <v>142</v>
       </c>
       <c r="B32" s="4">
         <v>1000</v>
@@ -1956,7 +1893,7 @@
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A33" s="9" t="s">
-        <v>165</v>
+        <v>143</v>
       </c>
       <c r="B33" s="4">
         <v>1000</v>
@@ -1997,7 +1934,7 @@
     </row>
     <row r="34" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A34" s="9" t="s">
-        <v>166</v>
+        <v>144</v>
       </c>
       <c r="B34" s="15">
         <v>1000</v>
@@ -2038,7 +1975,7 @@
     </row>
     <row r="36" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B36" t="s">
-        <v>169</v>
+        <v>147</v>
       </c>
     </row>
     <row r="37" spans="1:13" x14ac:dyDescent="0.25">
@@ -2081,7 +2018,7 @@
     </row>
     <row r="38" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A38" s="9" t="s">
-        <v>159</v>
+        <v>137</v>
       </c>
       <c r="B38" s="10">
         <v>610</v>
@@ -2122,7 +2059,7 @@
     </row>
     <row r="39" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A39" s="9" t="s">
-        <v>160</v>
+        <v>138</v>
       </c>
       <c r="B39" s="4">
         <v>660</v>
@@ -2163,7 +2100,7 @@
     </row>
     <row r="40" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A40" s="9" t="s">
-        <v>161</v>
+        <v>139</v>
       </c>
       <c r="B40" s="4">
         <v>669</v>
@@ -2204,7 +2141,7 @@
     </row>
     <row r="41" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A41" s="9" t="s">
-        <v>162</v>
+        <v>140</v>
       </c>
       <c r="B41" s="4">
         <v>665</v>
@@ -2245,7 +2182,7 @@
     </row>
     <row r="42" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A42" s="9" t="s">
-        <v>163</v>
+        <v>141</v>
       </c>
       <c r="B42" s="4">
         <v>600</v>
@@ -2286,7 +2223,7 @@
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A43" s="9" t="s">
-        <v>164</v>
+        <v>142</v>
       </c>
       <c r="B43" s="4">
         <v>634</v>
@@ -2327,7 +2264,7 @@
     </row>
     <row r="44" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A44" s="9" t="s">
-        <v>165</v>
+        <v>143</v>
       </c>
       <c r="B44" s="4">
         <v>627</v>
@@ -2368,7 +2305,7 @@
     </row>
     <row r="45" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A45" s="9" t="s">
-        <v>166</v>
+        <v>144</v>
       </c>
       <c r="B45" s="15">
         <v>615</v>
@@ -3053,293 +2990,293 @@
         <v>10</v>
       </c>
       <c r="B13" s="2"/>
-      <c r="C13" s="3" t="s">
+      <c r="C13" s="10" t="s">
         <v>134</v>
       </c>
-      <c r="D13" s="3" t="s">
+      <c r="D13" s="11" t="s">
+        <v>148</v>
+      </c>
+      <c r="E13" s="11" t="s">
+        <v>149</v>
+      </c>
+      <c r="F13" s="11" t="s">
+        <v>150</v>
+      </c>
+      <c r="G13" s="11" t="s">
+        <v>151</v>
+      </c>
+      <c r="H13" s="11" t="s">
+        <v>152</v>
+      </c>
+      <c r="I13" s="11" t="s">
+        <v>153</v>
+      </c>
+      <c r="J13" s="11" t="s">
+        <v>154</v>
+      </c>
+      <c r="K13" s="11" t="s">
+        <v>155</v>
+      </c>
+      <c r="L13" s="11" t="s">
+        <v>156</v>
+      </c>
+      <c r="M13" s="11" t="s">
+        <v>157</v>
+      </c>
+      <c r="N13" s="11" t="s">
+        <v>158</v>
+      </c>
+      <c r="O13" s="10" t="s">
+        <v>134</v>
+      </c>
+      <c r="P13" s="11" t="s">
+        <v>148</v>
+      </c>
+      <c r="Q13" s="11" t="s">
+        <v>149</v>
+      </c>
+      <c r="R13" s="11" t="s">
+        <v>150</v>
+      </c>
+      <c r="S13" s="11" t="s">
+        <v>151</v>
+      </c>
+      <c r="T13" s="11" t="s">
+        <v>152</v>
+      </c>
+      <c r="U13" s="11" t="s">
+        <v>153</v>
+      </c>
+      <c r="V13" s="11" t="s">
+        <v>154</v>
+      </c>
+      <c r="W13" s="11" t="s">
+        <v>155</v>
+      </c>
+      <c r="X13" s="11" t="s">
+        <v>156</v>
+      </c>
+      <c r="Y13" s="11" t="s">
+        <v>157</v>
+      </c>
+      <c r="Z13" s="11" t="s">
+        <v>158</v>
+      </c>
+      <c r="AA13" s="10" t="s">
+        <v>134</v>
+      </c>
+      <c r="AB13" s="11" t="s">
+        <v>148</v>
+      </c>
+      <c r="AC13" s="11" t="s">
+        <v>149</v>
+      </c>
+      <c r="AD13" s="11" t="s">
+        <v>150</v>
+      </c>
+      <c r="AE13" s="11" t="s">
+        <v>151</v>
+      </c>
+      <c r="AF13" s="11" t="s">
+        <v>152</v>
+      </c>
+      <c r="AG13" s="11" t="s">
+        <v>153</v>
+      </c>
+      <c r="AH13" s="11" t="s">
+        <v>154</v>
+      </c>
+      <c r="AI13" s="11" t="s">
+        <v>155</v>
+      </c>
+      <c r="AJ13" s="11" t="s">
+        <v>156</v>
+      </c>
+      <c r="AK13" s="11" t="s">
+        <v>157</v>
+      </c>
+      <c r="AL13" s="11" t="s">
+        <v>158</v>
+      </c>
+      <c r="AM13" s="10" t="s">
+        <v>134</v>
+      </c>
+      <c r="AN13" s="11" t="s">
+        <v>148</v>
+      </c>
+      <c r="AO13" s="11" t="s">
+        <v>149</v>
+      </c>
+      <c r="AP13" s="11" t="s">
+        <v>150</v>
+      </c>
+      <c r="AQ13" s="11" t="s">
+        <v>151</v>
+      </c>
+      <c r="AR13" s="11" t="s">
+        <v>152</v>
+      </c>
+      <c r="AS13" s="11" t="s">
+        <v>153</v>
+      </c>
+      <c r="AT13" s="11" t="s">
+        <v>154</v>
+      </c>
+      <c r="AU13" s="11" t="s">
+        <v>155</v>
+      </c>
+      <c r="AV13" s="11" t="s">
+        <v>156</v>
+      </c>
+      <c r="AW13" s="11" t="s">
+        <v>157</v>
+      </c>
+      <c r="AX13" s="11" t="s">
+        <v>158</v>
+      </c>
+      <c r="AY13" s="4" t="s">
         <v>135</v>
       </c>
-      <c r="E13" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="F13" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="G13" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="H13" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="I13" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="J13" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="K13" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="L13" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="M13" s="3" t="s">
-        <v>144</v>
-      </c>
-      <c r="N13" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="O13" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="P13" s="3" t="s">
+      <c r="AZ13" s="13" t="s">
+        <v>159</v>
+      </c>
+      <c r="BA13" s="13" t="s">
+        <v>160</v>
+      </c>
+      <c r="BB13" s="13" t="s">
+        <v>161</v>
+      </c>
+      <c r="BC13" s="13" t="s">
+        <v>162</v>
+      </c>
+      <c r="BD13" s="13" t="s">
+        <v>163</v>
+      </c>
+      <c r="BE13" s="13" t="s">
+        <v>164</v>
+      </c>
+      <c r="BF13" s="13" t="s">
+        <v>165</v>
+      </c>
+      <c r="BG13" s="13" t="s">
+        <v>166</v>
+      </c>
+      <c r="BH13" s="13" t="s">
+        <v>167</v>
+      </c>
+      <c r="BI13" s="13" t="s">
+        <v>168</v>
+      </c>
+      <c r="BJ13" s="13" t="s">
+        <v>169</v>
+      </c>
+      <c r="BK13" s="4" t="s">
         <v>135</v>
       </c>
-      <c r="Q13" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="R13" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="S13" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="T13" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="U13" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="V13" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="W13" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="X13" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="Y13" s="3" t="s">
-        <v>144</v>
-      </c>
-      <c r="Z13" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="AA13" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="AB13" s="3" t="s">
+      <c r="BL13" s="13" t="s">
+        <v>159</v>
+      </c>
+      <c r="BM13" s="13" t="s">
+        <v>160</v>
+      </c>
+      <c r="BN13" s="13" t="s">
+        <v>161</v>
+      </c>
+      <c r="BO13" s="13" t="s">
+        <v>162</v>
+      </c>
+      <c r="BP13" s="13" t="s">
+        <v>163</v>
+      </c>
+      <c r="BQ13" s="13" t="s">
+        <v>164</v>
+      </c>
+      <c r="BR13" s="13" t="s">
+        <v>165</v>
+      </c>
+      <c r="BS13" s="13" t="s">
+        <v>166</v>
+      </c>
+      <c r="BT13" s="13" t="s">
+        <v>167</v>
+      </c>
+      <c r="BU13" s="13" t="s">
+        <v>168</v>
+      </c>
+      <c r="BV13" s="13" t="s">
+        <v>169</v>
+      </c>
+      <c r="BW13" s="4" t="s">
         <v>135</v>
       </c>
-      <c r="AC13" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="AD13" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="AE13" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="AF13" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="AG13" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="AH13" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="AI13" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="AJ13" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="AK13" s="3" t="s">
-        <v>144</v>
-      </c>
-      <c r="AL13" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="AM13" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="AN13" s="3" t="s">
+      <c r="BX13" s="13" t="s">
+        <v>159</v>
+      </c>
+      <c r="BY13" s="13" t="s">
+        <v>160</v>
+      </c>
+      <c r="BZ13" s="13" t="s">
+        <v>161</v>
+      </c>
+      <c r="CA13" s="13" t="s">
+        <v>162</v>
+      </c>
+      <c r="CB13" s="13" t="s">
+        <v>163</v>
+      </c>
+      <c r="CC13" s="13" t="s">
+        <v>164</v>
+      </c>
+      <c r="CD13" s="13" t="s">
+        <v>165</v>
+      </c>
+      <c r="CE13" s="13" t="s">
+        <v>166</v>
+      </c>
+      <c r="CF13" s="13" t="s">
+        <v>167</v>
+      </c>
+      <c r="CG13" s="13" t="s">
+        <v>168</v>
+      </c>
+      <c r="CH13" s="13" t="s">
+        <v>169</v>
+      </c>
+      <c r="CI13" s="4" t="s">
         <v>135</v>
       </c>
-      <c r="AO13" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="AP13" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="AQ13" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="AR13" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="AS13" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="AT13" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="AU13" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="AV13" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="AW13" s="3" t="s">
-        <v>144</v>
-      </c>
-      <c r="AX13" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="AY13" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="AZ13" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="BA13" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="BB13" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="BC13" s="3" t="s">
-        <v>150</v>
-      </c>
-      <c r="BD13" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="BE13" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="BF13" s="3" t="s">
-        <v>153</v>
-      </c>
-      <c r="BG13" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="BH13" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="BI13" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="BJ13" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="BK13" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="BL13" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="BM13" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="BN13" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="BO13" s="3" t="s">
-        <v>150</v>
-      </c>
-      <c r="BP13" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="BQ13" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="BR13" s="3" t="s">
-        <v>153</v>
-      </c>
-      <c r="BS13" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="BT13" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="BU13" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="BV13" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="BW13" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="BX13" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="BY13" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="BZ13" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="CA13" s="3" t="s">
-        <v>150</v>
-      </c>
-      <c r="CB13" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="CC13" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="CD13" s="3" t="s">
-        <v>153</v>
-      </c>
-      <c r="CE13" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="CF13" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="CG13" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="CH13" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="CI13" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="CJ13" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="CK13" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="CL13" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="CM13" s="3" t="s">
-        <v>150</v>
-      </c>
-      <c r="CN13" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="CO13" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="CP13" s="3" t="s">
-        <v>153</v>
-      </c>
-      <c r="CQ13" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="CR13" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="CS13" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="CT13" s="4" t="s">
-        <v>157</v>
+      <c r="CJ13" s="13" t="s">
+        <v>159</v>
+      </c>
+      <c r="CK13" s="13" t="s">
+        <v>160</v>
+      </c>
+      <c r="CL13" s="13" t="s">
+        <v>161</v>
+      </c>
+      <c r="CM13" s="13" t="s">
+        <v>162</v>
+      </c>
+      <c r="CN13" s="13" t="s">
+        <v>163</v>
+      </c>
+      <c r="CO13" s="13" t="s">
+        <v>164</v>
+      </c>
+      <c r="CP13" s="13" t="s">
+        <v>165</v>
+      </c>
+      <c r="CQ13" s="13" t="s">
+        <v>166</v>
+      </c>
+      <c r="CR13" s="13" t="s">
+        <v>167</v>
+      </c>
+      <c r="CS13" s="13" t="s">
+        <v>168</v>
+      </c>
+      <c r="CT13" s="13" t="s">
+        <v>169</v>
       </c>
     </row>
     <row r="14" spans="1:98" ht="30" x14ac:dyDescent="0.25">
